--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129626534</v>
+        <v>129626536</v>
       </c>
       <c r="B2" t="n">
-        <v>4779</v>
+        <v>79663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543137</v>
+        <v>543099</v>
       </c>
       <c r="R2" t="n">
-        <v>6535482</v>
+        <v>6535479</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +785,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129626536</v>
+        <v>129626534</v>
       </c>
       <c r="B3" t="n">
-        <v>79663</v>
+        <v>4779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543099</v>
+        <v>543137</v>
       </c>
       <c r="R3" t="n">
-        <v>6535479</v>
+        <v>6535482</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129626536</v>
       </c>
       <c r="B2" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129626537</v>
       </c>
       <c r="B4" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129626536</v>
+        <v>129626534</v>
       </c>
       <c r="B2" t="n">
-        <v>79689</v>
+        <v>4779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>102306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543099</v>
+        <v>543137</v>
       </c>
       <c r="R2" t="n">
-        <v>6535479</v>
+        <v>6535482</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,43 +791,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129626534</v>
+        <v>129626536</v>
       </c>
       <c r="B3" t="n">
-        <v>4779</v>
+        <v>79694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543137</v>
+        <v>543099</v>
       </c>
       <c r="R3" t="n">
-        <v>6535482</v>
+        <v>6535479</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
         <v>129626537</v>
       </c>
       <c r="B4" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129626534</v>
+        <v>129626536</v>
       </c>
       <c r="B2" t="n">
-        <v>4779</v>
+        <v>79695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543137</v>
+        <v>543099</v>
       </c>
       <c r="R2" t="n">
-        <v>6535482</v>
+        <v>6535479</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +785,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129626536</v>
+        <v>129626534</v>
       </c>
       <c r="B3" t="n">
-        <v>79694</v>
+        <v>4779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543099</v>
+        <v>543137</v>
       </c>
       <c r="R3" t="n">
-        <v>6535479</v>
+        <v>6535482</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
         <v>129626537</v>
       </c>
       <c r="B4" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129626536</v>
+        <v>129626534</v>
       </c>
       <c r="B2" t="n">
-        <v>79695</v>
+        <v>4779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>102306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543099</v>
+        <v>543137</v>
       </c>
       <c r="R2" t="n">
-        <v>6535479</v>
+        <v>6535482</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,43 +791,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129626534</v>
+        <v>129626536</v>
       </c>
       <c r="B3" t="n">
-        <v>4779</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543137</v>
+        <v>543099</v>
       </c>
       <c r="R3" t="n">
-        <v>6535482</v>
+        <v>6535479</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
         <v>129626537</v>
       </c>
       <c r="B4" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129626534</v>
+        <v>129626536</v>
       </c>
       <c r="B2" t="n">
-        <v>4779</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543137</v>
+        <v>543099</v>
       </c>
       <c r="R2" t="n">
-        <v>6535482</v>
+        <v>6535479</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +785,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129626536</v>
+        <v>129626534</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>4779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543099</v>
+        <v>543137</v>
       </c>
       <c r="R3" t="n">
-        <v>6535479</v>
+        <v>6535482</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129626537</v>
       </c>
       <c r="B4" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129626536</v>
+        <v>129626534</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>4779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>102306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543099</v>
+        <v>543137</v>
       </c>
       <c r="R2" t="n">
-        <v>6535479</v>
+        <v>6535482</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,43 +791,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129626534</v>
+        <v>129626536</v>
       </c>
       <c r="B3" t="n">
-        <v>4779</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543137</v>
+        <v>543099</v>
       </c>
       <c r="R3" t="n">
-        <v>6535482</v>
+        <v>6535479</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
         <v>129626537</v>
       </c>
       <c r="B4" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129626536</v>
+        <v>129626534</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>4779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>102306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543099</v>
+        <v>543137</v>
       </c>
       <c r="R2" t="n">
-        <v>6535479</v>
+        <v>6535482</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,43 +791,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129626534</v>
+        <v>129626536</v>
       </c>
       <c r="B3" t="n">
-        <v>4779</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543137</v>
+        <v>543099</v>
       </c>
       <c r="R3" t="n">
-        <v>6535482</v>
+        <v>6535479</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129626534</v>
+        <v>129626536</v>
       </c>
       <c r="B2" t="n">
-        <v>4779</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543137</v>
+        <v>543099</v>
       </c>
       <c r="R2" t="n">
-        <v>6535482</v>
+        <v>6535479</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +785,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129626536</v>
+        <v>129626534</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>4779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543099</v>
+        <v>543137</v>
       </c>
       <c r="R3" t="n">
-        <v>6535479</v>
+        <v>6535482</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
         <v>129626537</v>
       </c>
       <c r="B4" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129626536</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129626537</v>
       </c>
       <c r="B4" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129626536</v>
       </c>
       <c r="B2" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129626537</v>
       </c>
       <c r="B4" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1010,6 +1010,558 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130103423</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bladkärrsbäcken, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>543075</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6535460</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130103409</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78489</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>213</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedspik</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Calicium abietinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bladkärrsbäcken, Bladkärrsbäcken, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>543183</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6535486</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130103420</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96304</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bladkärrsbäcken, Bladkärrsbäcken, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>543191</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6535533</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130103411</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78755</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>353</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bladkärrsbäcken, Bladkärrsbäcken, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>543288</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6535573</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130103416</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bladkärrsbäcken, Bladkärrsbäcken, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>543207</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6535582</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -1236,7 +1236,7 @@
         <v>130103420</v>
       </c>
       <c r="B7" t="n">
-        <v>96320</v>
+        <v>96322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>130114670</v>
       </c>
       <c r="B11" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -1015,7 +1015,7 @@
         <v>130103423</v>
       </c>
       <c r="B5" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130103409</v>
       </c>
       <c r="B6" t="n">
-        <v>78495</v>
+        <v>78580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>130103420</v>
       </c>
       <c r="B7" t="n">
-        <v>96322</v>
+        <v>96409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>130103411</v>
       </c>
       <c r="B8" t="n">
-        <v>78761</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>130103416</v>
       </c>
       <c r="B9" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>130114844</v>
       </c>
       <c r="B10" t="n">
-        <v>78761</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>130114670</v>
       </c>
       <c r="B11" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -1015,7 +1015,7 @@
         <v>130103423</v>
       </c>
       <c r="B5" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
         <v>130103409</v>
       </c>
       <c r="B6" t="n">
-        <v>78580</v>
+        <v>78583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
         <v>130103420</v>
       </c>
       <c r="B7" t="n">
-        <v>96409</v>
+        <v>96412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
         <v>130103411</v>
       </c>
       <c r="B8" t="n">
-        <v>78846</v>
+        <v>78849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1457,7 +1457,7 @@
         <v>130103416</v>
       </c>
       <c r="B9" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1567,7 +1567,7 @@
         <v>130114844</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>78849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>130114670</v>
       </c>
       <c r="B11" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>130114844</v>
       </c>
       <c r="B10" t="n">
-        <v>78849</v>
+        <v>78875</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>130114670</v>
       </c>
       <c r="B11" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 53847-2025 artfynd.xlsx
+++ b/artfynd/A 53847-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129626536</v>
+        <v>129626537</v>
       </c>
       <c r="B2" t="n">
-        <v>79706</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543099</v>
+        <v>543171</v>
       </c>
       <c r="R2" t="n">
-        <v>6535479</v>
+        <v>6535478</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,43 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129626534</v>
+        <v>130103409</v>
       </c>
       <c r="B3" t="n">
-        <v>4779</v>
+        <v>78727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>213</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Calicium abietinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543137</v>
+        <v>543183</v>
       </c>
       <c r="R3" t="n">
-        <v>6535482</v>
+        <v>6535486</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,17 +889,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Birgitta Hamstedt</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129626537</v>
+        <v>130103411</v>
       </c>
       <c r="B4" t="n">
-        <v>97043</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,27 +907,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543171</v>
+        <v>543288</v>
       </c>
       <c r="R4" t="n">
-        <v>6535478</v>
+        <v>6535573</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,22 +964,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,17 +999,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Birgitta Hamstedt</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130103423</v>
+        <v>130114844</v>
       </c>
       <c r="B5" t="n">
-        <v>79802</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,41 +1017,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bladkärrsbäcken, Srm</t>
+          <t>Marsjö-Vittorp 2 km s, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543075</v>
+        <v>543293</v>
       </c>
       <c r="R5" t="n">
-        <v>6535460</v>
+        <v>6535563</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,76 +1085,78 @@
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Talldominerad barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
+          <t>Bo Karlsson, Rolf Olsson, Eva Grusell, Göran Ekström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130103409</v>
+        <v>130103420</v>
       </c>
       <c r="B6" t="n">
-        <v>78583</v>
+        <v>96601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>213</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedspik</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium abietinum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543183</v>
+        <v>543191</v>
       </c>
       <c r="R6" t="n">
-        <v>6535486</v>
+        <v>6535533</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1196,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,59 +1229,66 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130103420</v>
+        <v>130114670</v>
       </c>
       <c r="B7" t="n">
-        <v>96412</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bladkärrsbäcken, Bladkärrsbäcken, Srm</t>
+          <t>Marsjö-Vittorp, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543191</v>
+        <v>543167</v>
       </c>
       <c r="R7" t="n">
-        <v>6535533</v>
+        <v>6535611</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,49 +1315,50 @@
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Talldominerad barrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130103411</v>
+        <v>130114699</v>
       </c>
       <c r="B8" t="n">
-        <v>78849</v>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,40 +1366,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bladkärrsbäcken, Bladkärrsbäcken, Srm</t>
+          <t>Marsjö-Vittorp 2 km s, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543288</v>
+        <v>543198</v>
       </c>
       <c r="R8" t="n">
-        <v>6535573</v>
+        <v>6535650</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,49 +1434,50 @@
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Talldominerad barrskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
+          <t>Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130103416</v>
+        <v>129626536</v>
       </c>
       <c r="B9" t="n">
-        <v>79802</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,13 +1512,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543207</v>
+        <v>543099</v>
       </c>
       <c r="R9" t="n">
-        <v>6535582</v>
+        <v>6535479</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,22 +1542,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,17 +1577,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Eva Grusell, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Birgitta Hamstedt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130114844</v>
+        <v>130103416</v>
       </c>
       <c r="B10" t="n">
-        <v>78875</v>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,48 +1595,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Marsjö-Vittorp 2 km s, Srm</t>
+          <t>Bladkärrsbäcken, Bladkärrsbäcken, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543293</v>
+        <v>543207</v>
       </c>
       <c r="R10" t="n">
-        <v>6535563</v>
+        <v>6535582</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1643,99 +1655,91 @@
           <t>2025-12-12</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Talldominerad barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Rolf Olsson, Eva Grusell, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130114670</v>
+        <v>130103423</v>
       </c>
       <c r="B11" t="n">
-        <v>93039</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Marsjö-Vittorp, Srm</t>
+          <t>Bladkärrsbäcken, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543167</v>
+        <v>543075</v>
       </c>
       <c r="R11" t="n">
-        <v>6535611</v>
+        <v>6535460</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1762,50 +1766,49 @@
           <t>2025-12-12</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Talldominerad barrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130114877</v>
+        <v>129626534</v>
       </c>
       <c r="B12" t="n">
-        <v>4779</v>
+        <v>4781</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,29 +1833,29 @@
           <t>(Duftschmid, 1825)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Marsjö-Vittorp 2 km s, Srm</t>
+          <t>Bladkärrsbäcken, Bladkärrsbäcken, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543144</v>
+        <v>543137</v>
       </c>
       <c r="R12" t="n">
-        <v>6535515</v>
+        <v>6535482</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1876,17 +1879,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>i gammal grov levande gran</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,32 +1903,143 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Talldominerad barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Birgitta Hamstedt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130114877</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Marsjö-Vittorp 2 km s, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>543144</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6535515</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>i gammal grov levande gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Talldominerad barrskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Bo Karlsson, Rolf Olsson, Eva Grusell, Göran Ekström</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
